--- a/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,57; 94,42</t>
+          <t>68,38; 93,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,69; 93,88</t>
+          <t>66,07; 94,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,9; 92,05</t>
+          <t>74,02; 91,41</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,18; 87,47</t>
+          <t>75,25; 87,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,21; 78,46</t>
+          <t>66,71; 78,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,64; 81,39</t>
+          <t>72,8; 81,89</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,04; 71,21</t>
+          <t>54,59; 70,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,76; 75,92</t>
+          <t>58,23; 75,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,87; 70,66</t>
+          <t>59,18; 71,48</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,06; 82,47</t>
+          <t>71,64; 82,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,13; 77,15</t>
+          <t>67,77; 76,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,0; 78,24</t>
+          <t>71,34; 78,36</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23958</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51872</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>19414; 26533</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21838; 31080</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45481; 56165</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>175045</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>189772</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>364817</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>163067; 190338</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>172257; 202586</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>345744; 388927</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>53255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>117258</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>46424; 60129</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55239; 71844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>106468; 128590</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>252258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>281689</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>533947</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>236495; 272515</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>261692; 296993</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>510978; 561306</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,38; 93,46</t>
+          <t>68,7; 93,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,07; 94,03</t>
+          <t>68,28; 94,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,02; 91,41</t>
+          <t>73,92; 91,66</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,25; 87,84</t>
+          <t>75,43; 86,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,71; 78,45</t>
+          <t>67,37; 78,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,8; 81,89</t>
+          <t>72,27; 81,65</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,59; 70,71</t>
+          <t>53,45; 70,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,23; 75,73</t>
+          <t>58,94; 75,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,18; 71,48</t>
+          <t>58,97; 71,22</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,64; 82,55</t>
+          <t>72,23; 82,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,77; 76,91</t>
+          <t>68,07; 77,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,34; 78,36</t>
+          <t>71,18; 78,28</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19414; 26533</t>
+          <t>19505; 26653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21838; 31080</t>
+          <t>22568; 31231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45481; 56165</t>
+          <t>45420; 56317</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>163067; 190338</t>
+          <t>163444; 188495</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172257; 202586</t>
+          <t>173960; 203403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>345744; 388927</t>
+          <t>343213; 387791</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46424; 60129</t>
+          <t>45453; 59901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55239; 71844</t>
+          <t>55911; 72022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106468; 128590</t>
+          <t>106098; 128132</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>236495; 272515</t>
+          <t>238447; 271852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>261692; 296993</t>
+          <t>262850; 297538</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>510978; 561306</t>
+          <t>509862; 560684</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,7; 93,88</t>
+          <t>63,44; 93,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,28; 94,49</t>
+          <t>63,95; 92,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,92; 91,66</t>
+          <t>71,72; 90,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,43; 86,99</t>
+          <t>67,54; 78,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,37; 78,77</t>
+          <t>72,71; 82,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,27; 81,65</t>
+          <t>71,42; 78,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,45; 70,44</t>
+          <t>58,88; 75,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,94; 75,92</t>
+          <t>53,41; 70,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,97; 71,22</t>
+          <t>58,72; 70,44</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,23; 82,35</t>
+          <t>68,21; 77,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,07; 77,05</t>
+          <t>69,39; 77,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,18; 78,28</t>
+          <t>69,89; 76,15</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>44495</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19505; 26653</t>
+          <t>19218; 28335</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22568; 31231</t>
+          <t>15063; 21823</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45420; 56317</t>
+          <t>38621; 48905</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>233</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>175045</t>
+          <t>175883</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>189772</t>
+          <t>149014</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364817</t>
+          <t>324897</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>163444; 188495</t>
+          <t>161565; 188181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173960; 203403</t>
+          <t>139057; 158557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>343213; 387791</t>
+          <t>307430; 339203</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>59544</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>112546</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45453; 59901</t>
+          <t>52084; 66995</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55911; 72022</t>
+          <t>45656; 60535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106098; 128132</t>
+          <t>102136; 122513</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>345</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>252258</t>
+          <t>260739</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221199</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>533947</t>
+          <t>481939</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238447; 271852</t>
+          <t>244156; 275967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>262850; 297538</t>
+          <t>208351; 233665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>509862; 560684</t>
+          <t>460074; 501237</t>
         </is>
       </c>
     </row>
